--- a/data-raw/preferenties/Preferentietabel 24 totaal-fosfor in waterbodem.xlsx
+++ b/data-raw/preferenties/Preferentietabel 24 totaal-fosfor in waterbodem.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/24f2756d9d8bedf6/Documents/ZZP/Projecten - lopend/Fase 2 - W^0W/Achtergronddocument/Preferentietabellen achtergrondrapport/Bodem/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R\waterplanten\data-raw\preferenties\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{A52708DD-968C-4084-B679-D619934126B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5379AEB9-DBBE-4B12-AB9A-313E537157B7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5FF4D22-09FE-4E85-97B6-FA65FB0B76DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19298" yWindow="-4005" windowWidth="19396" windowHeight="11475" xr2:uid="{76198A1B-E75D-41FE-B4E1-38438BBE6DC1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{76198A1B-E75D-41FE-B4E1-38438BBE6DC1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -38,11 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="247">
   <si>
-    <t>0_x000D_
- - _x000D_
-100</t>
-  </si>
-  <si>
     <t>100_x000D_
  - _x000D_
 500</t>
@@ -58,11 +53,6 @@
 2500</t>
   </si>
   <si>
-    <t>2500_x000D_
- - _x000D_
-Inf</t>
-  </si>
-  <si>
     <t>ind</t>
   </si>
   <si>
@@ -787,6 +777,14 @@
   </si>
   <si>
     <t>ind = indicatiegewicht, gemod. chi = gemodificeerde chi-waarde; gewogen gemid. = gewogen gemiddelde; opt =  optimum; voor uitleg, zie hoofdstuk 8 van dit rapport</t>
+  </si>
+  <si>
+    <t>0
+ - 
+100</t>
+  </si>
+  <si>
+    <t>&gt; 2500</t>
   </si>
 </sst>
 </file>
@@ -885,7 +883,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -900,12 +898,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Kantoorthema">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1230,17 +1224,17 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="3"/>
@@ -1266,48 +1260,48 @@
     </row>
     <row r="5" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="D5" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="J5" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="K5" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J5" s="9" t="s">
+      <c r="L5" s="8" t="s">
         <v>243</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C6" s="1">
         <v>71</v>
@@ -1328,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J6" s="6">
         <v>95.41</v>
@@ -1342,10 +1336,10 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C7" s="1">
         <v>12</v>
@@ -1366,7 +1360,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J7" s="6">
         <v>105.12</v>
@@ -1380,10 +1374,10 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C8" s="1">
         <v>25</v>
@@ -1404,7 +1398,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J8" s="6">
         <v>105.77</v>
@@ -1418,10 +1412,10 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" s="1">
         <v>23</v>
@@ -1442,7 +1436,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J9" s="6">
         <v>151.57</v>
@@ -1456,10 +1450,10 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C10" s="1">
         <v>21</v>
@@ -1480,7 +1474,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J10" s="6">
         <v>154.57</v>
@@ -1494,10 +1488,10 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1">
         <v>7</v>
@@ -1518,7 +1512,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J11" s="6">
         <v>155.19999999999999</v>
@@ -1532,10 +1526,10 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C12" s="1">
         <v>13</v>
@@ -1556,7 +1550,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J12" s="6">
         <v>159.27000000000001</v>
@@ -1570,10 +1564,10 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C13" s="1">
         <v>24</v>
@@ -1594,7 +1588,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J13" s="6">
         <v>161.41999999999999</v>
@@ -1608,10 +1602,10 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C14" s="1">
         <v>32</v>
@@ -1632,7 +1626,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J14" s="6">
         <v>163.03</v>
@@ -1646,10 +1640,10 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C15" s="1">
         <v>9</v>
@@ -1670,7 +1664,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J15" s="6">
         <v>169.36</v>
@@ -1684,10 +1678,10 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C16" s="1">
         <v>25</v>
@@ -1708,7 +1702,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J16" s="6">
         <v>191.45</v>
@@ -1722,10 +1716,10 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C17" s="1">
         <v>12</v>
@@ -1746,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J17" s="6">
         <v>198.72</v>
@@ -1760,10 +1754,10 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C18" s="1">
         <v>31</v>
@@ -1784,7 +1778,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J18" s="6">
         <v>208.89</v>
@@ -1798,10 +1792,10 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C19" s="1">
         <v>41</v>
@@ -1822,7 +1816,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J19" s="6">
         <v>221.16</v>
@@ -1836,10 +1830,10 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C20" s="1">
         <v>26</v>
@@ -1860,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J20" s="6">
         <v>226.02</v>
@@ -1874,10 +1868,10 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C21" s="1">
         <v>39</v>
@@ -1898,7 +1892,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J21" s="6">
         <v>236.37</v>
@@ -1912,10 +1906,10 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C22" s="1">
         <v>56</v>
@@ -1936,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J22" s="6">
         <v>242.17</v>
@@ -1950,10 +1944,10 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C23" s="1">
         <v>19</v>
@@ -1974,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J23" s="6">
         <v>252.33</v>
@@ -1988,10 +1982,10 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C24" s="1">
         <v>12</v>
@@ -2012,7 +2006,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J24" s="6">
         <v>257.92</v>
@@ -2026,10 +2020,10 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C25" s="1">
         <v>6</v>
@@ -2050,7 +2044,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J25" s="6">
         <v>261.19</v>
@@ -2064,10 +2058,10 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C26" s="1">
         <v>18</v>
@@ -2088,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J26" s="6">
         <v>261.43</v>
@@ -2102,10 +2096,10 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C27" s="1">
         <v>25</v>
@@ -2126,7 +2120,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J27" s="6">
         <v>280.26</v>
@@ -2140,10 +2134,10 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B28" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C28" s="1">
         <v>51</v>
@@ -2164,7 +2158,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J28" s="6">
         <v>306.16000000000003</v>
@@ -2178,10 +2172,10 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C29" s="1">
         <v>26</v>
@@ -2202,7 +2196,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J29" s="6">
         <v>309.10000000000002</v>
@@ -2216,10 +2210,10 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B30" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C30" s="1">
         <v>15</v>
@@ -2240,7 +2234,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J30" s="6">
         <v>321.45</v>
@@ -2254,10 +2248,10 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B31" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C31" s="1">
         <v>19</v>
@@ -2278,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J31" s="6">
         <v>324.64999999999998</v>
@@ -2292,10 +2286,10 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B32" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C32" s="1">
         <v>5</v>
@@ -2316,7 +2310,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J32" s="6">
         <v>327.39999999999998</v>
@@ -2330,10 +2324,10 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B33" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C33" s="1">
         <v>10</v>
@@ -2354,7 +2348,7 @@
         <v>0</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J33" s="6">
         <v>327.57</v>
@@ -2368,10 +2362,10 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B34" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C34" s="1">
         <v>31</v>
@@ -2392,7 +2386,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J34" s="6">
         <v>330.78</v>
@@ -2406,10 +2400,10 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C35" s="1">
         <v>50</v>
@@ -2430,7 +2424,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J35" s="6">
         <v>333.22</v>
@@ -2444,10 +2438,10 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B36" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C36" s="1">
         <v>35</v>
@@ -2468,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J36" s="6">
         <v>338</v>
@@ -2482,10 +2476,10 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B37" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C37" s="1">
         <v>16</v>
@@ -2506,7 +2500,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J37" s="6">
         <v>340.26</v>
@@ -2520,10 +2514,10 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B38" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C38" s="1">
         <v>20</v>
@@ -2544,7 +2538,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J38" s="6">
         <v>348.35</v>
@@ -2558,10 +2552,10 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B39" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C39" s="1">
         <v>13</v>
@@ -2582,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J39" s="6">
         <v>375.93</v>
@@ -2596,10 +2590,10 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B40" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C40" s="1">
         <v>63</v>
@@ -2620,7 +2614,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J40" s="6">
         <v>395.05</v>
@@ -2634,10 +2628,10 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B41" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C41" s="1">
         <v>30</v>
@@ -2658,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J41" s="6">
         <v>412.01</v>
@@ -2672,10 +2666,10 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B42" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C42" s="1">
         <v>4</v>
@@ -2696,7 +2690,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J42" s="6">
         <v>418.45</v>
@@ -2710,10 +2704,10 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C43" s="1">
         <v>58</v>
@@ -2734,7 +2728,7 @@
         <v>10.31</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J43" s="6">
         <v>468.76</v>
@@ -2748,10 +2742,10 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B44" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C44" s="1">
         <v>11</v>
@@ -2772,7 +2766,7 @@
         <v>0</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J44" s="6">
         <v>478.23</v>
@@ -2786,10 +2780,10 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B45" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C45" s="1">
         <v>7</v>
@@ -2810,7 +2804,7 @@
         <v>0</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J45" s="6">
         <v>531.73</v>
@@ -2824,10 +2818,10 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C46" s="1">
         <v>38</v>
@@ -2848,7 +2842,7 @@
         <v>15.39</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J46" s="6">
         <v>543.16999999999996</v>
@@ -2862,10 +2856,10 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B47" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C47" s="1">
         <v>25</v>
@@ -2886,7 +2880,7 @@
         <v>0</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J47" s="6">
         <v>554.66999999999996</v>
@@ -2900,10 +2894,10 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B48" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C48" s="1">
         <v>16</v>
@@ -2924,7 +2918,7 @@
         <v>0</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J48" s="6">
         <v>561.48</v>
@@ -2938,10 +2932,10 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B49" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C49" s="1">
         <v>50</v>
@@ -2962,7 +2956,7 @@
         <v>12.91</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J49" s="6">
         <v>581.69000000000005</v>
@@ -2976,10 +2970,10 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B50" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C50" s="1">
         <v>13</v>
@@ -3000,7 +2994,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J50" s="6">
         <v>584.34</v>
@@ -3014,10 +3008,10 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B51" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C51" s="1">
         <v>21</v>
@@ -3038,7 +3032,7 @@
         <v>0</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J51" s="6">
         <v>623.79</v>
@@ -3052,10 +3046,10 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B52" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C52" s="1">
         <v>23</v>
@@ -3076,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J52" s="6">
         <v>639.9</v>
@@ -3090,10 +3084,10 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B53" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C53" s="1">
         <v>31</v>
@@ -3114,7 +3108,7 @@
         <v>18.64</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J53" s="6">
         <v>647.25</v>
@@ -3128,10 +3122,10 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B54" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C54" s="1">
         <v>12</v>
@@ -3152,7 +3146,7 @@
         <v>0</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J54" s="6">
         <v>648.92999999999995</v>
@@ -3166,10 +3160,10 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B55" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C55" s="1">
         <v>25</v>
@@ -3190,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J55" s="6">
         <v>694.94</v>
@@ -3204,10 +3198,10 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B56" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C56" s="1">
         <v>64</v>
@@ -3228,7 +3222,7 @@
         <v>17.920000000000002</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J56" s="6">
         <v>754.19</v>
@@ -3242,10 +3236,10 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B57" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C57" s="1">
         <v>35</v>
@@ -3266,7 +3260,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J57" s="6">
         <v>762.75</v>
@@ -3280,10 +3274,10 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B58" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C58" s="1">
         <v>15</v>
@@ -3304,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J58" s="6">
         <v>784.91</v>
@@ -3318,10 +3312,10 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B59" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C59" s="1">
         <v>31</v>
@@ -3342,7 +3336,7 @@
         <v>0</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J59" s="6">
         <v>926.65</v>
@@ -3356,10 +3350,10 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B60" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C60" s="1">
         <v>5</v>
@@ -3380,7 +3374,7 @@
         <v>0</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J60" s="6">
         <v>968.96</v>
@@ -3394,10 +3388,10 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B61" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C61" s="1">
         <v>6</v>
@@ -3418,7 +3412,7 @@
         <v>0</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J61" s="6">
         <v>1047.78</v>
@@ -3432,10 +3426,10 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B62" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C62" s="1">
         <v>11</v>
@@ -3456,7 +3450,7 @@
         <v>0</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J62" s="6">
         <v>1179.76</v>
@@ -3470,10 +3464,10 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B63" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C63" s="1">
         <v>31</v>
@@ -3494,7 +3488,7 @@
         <v>18.260000000000002</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J63" s="6">
         <v>1221.45</v>
@@ -3508,10 +3502,10 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B64" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C64" s="1">
         <v>34</v>
@@ -3532,7 +3526,7 @@
         <v>13.94</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J64" s="6">
         <v>1631.31</v>
@@ -3546,10 +3540,10 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B65" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C65" s="1">
         <v>10</v>
@@ -3570,7 +3564,7 @@
         <v>48.38</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J65" s="6">
         <v>1769.57</v>
@@ -3584,10 +3578,10 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B66" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C66" s="1">
         <v>47</v>
@@ -3608,7 +3602,7 @@
         <v>49.62</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J66" s="6">
         <v>1792.95</v>
@@ -3622,10 +3616,10 @@
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B67" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C67" s="1">
         <v>24</v>
@@ -3646,7 +3640,7 @@
         <v>46.8</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J67" s="6">
         <v>1841.99</v>
@@ -3660,10 +3654,10 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B68" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C68" s="1">
         <v>25</v>
@@ -3684,7 +3678,7 @@
         <v>59.03</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J68" s="6">
         <v>2189.11</v>
@@ -3698,10 +3692,10 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B69" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C69" s="1">
         <v>17</v>
@@ -3722,7 +3716,7 @@
         <v>0</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J69" s="6">
         <v>378.58</v>
@@ -3736,10 +3730,10 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B70" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C70" s="1">
         <v>13</v>
@@ -3760,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J70" s="6">
         <v>434.57</v>
@@ -3774,10 +3768,10 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B71" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C71" s="1">
         <v>85</v>
@@ -3798,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J71" s="6">
         <v>443.95</v>
@@ -3812,10 +3806,10 @@
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B72" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C72" s="1">
         <v>18</v>
@@ -3836,7 +3830,7 @@
         <v>0</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J72" s="6">
         <v>475.9</v>
@@ -3850,10 +3844,10 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B73" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C73" s="1">
         <v>61</v>
@@ -3874,7 +3868,7 @@
         <v>0</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J73" s="6">
         <v>488.79</v>
@@ -3888,10 +3882,10 @@
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B74" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C74" s="1">
         <v>39</v>
@@ -3912,7 +3906,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J74" s="6">
         <v>491.86</v>
@@ -3926,10 +3920,10 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="10" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B75" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C75" s="1">
         <v>19</v>
@@ -3950,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J75" s="6">
         <v>502.61</v>
@@ -3964,10 +3958,10 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="10" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B76" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C76" s="1">
         <v>11</v>
@@ -3988,7 +3982,7 @@
         <v>0</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J76" s="6">
         <v>523.1</v>
@@ -4002,10 +3996,10 @@
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="10" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B77" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C77" s="1">
         <v>35</v>
@@ -4026,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J77" s="6">
         <v>567.70000000000005</v>
@@ -4040,10 +4034,10 @@
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="10" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B78" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C78" s="1">
         <v>127</v>
@@ -4064,7 +4058,7 @@
         <v>5.67</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J78" s="6">
         <v>568.02</v>
@@ -4078,10 +4072,10 @@
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="10" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B79" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C79" s="1">
         <v>15</v>
@@ -4102,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J79" s="6">
         <v>599.64</v>
@@ -4116,10 +4110,10 @@
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" s="10" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B80" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C80" s="1">
         <v>19</v>
@@ -4140,7 +4134,7 @@
         <v>0</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J80" s="6">
         <v>628.39</v>
@@ -4154,10 +4148,10 @@
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" s="10" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B81" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C81" s="1">
         <v>20</v>
@@ -4178,7 +4172,7 @@
         <v>0</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J81" s="6">
         <v>641.52</v>
@@ -4192,10 +4186,10 @@
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B82" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C82" s="1">
         <v>70</v>
@@ -4216,7 +4210,7 @@
         <v>10.37</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J82" s="6">
         <v>659.95</v>
@@ -4230,10 +4224,10 @@
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" s="10" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B83" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C83" s="1">
         <v>60</v>
@@ -4254,7 +4248,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J83" s="6">
         <v>678.69</v>
@@ -4268,10 +4262,10 @@
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B84" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C84" s="1">
         <v>16</v>
@@ -4292,7 +4286,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J84" s="6">
         <v>767.42</v>
@@ -4306,10 +4300,10 @@
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" s="10" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B85" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C85" s="1">
         <v>82</v>
@@ -4330,7 +4324,7 @@
         <v>8.0299999999999994</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J85" s="6">
         <v>833.2</v>
@@ -4344,10 +4338,10 @@
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" s="10" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B86" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C86" s="1">
         <v>14</v>
@@ -4368,7 +4362,7 @@
         <v>0</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J86" s="6">
         <v>906.8</v>
@@ -4382,10 +4376,10 @@
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" s="10" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B87" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C87" s="1">
         <v>41</v>
@@ -4406,7 +4400,7 @@
         <v>15.31</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J87" s="6">
         <v>979.79</v>
@@ -4420,10 +4414,10 @@
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" s="10" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B88" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C88" s="1">
         <v>59</v>
@@ -4444,7 +4438,7 @@
         <v>10.74</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J88" s="6">
         <v>1002.37</v>
@@ -4458,10 +4452,10 @@
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" s="10" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B89" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C89" s="1">
         <v>50</v>
@@ -4482,7 +4476,7 @@
         <v>12.02</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J89" s="6">
         <v>1030.5899999999999</v>
@@ -4496,10 +4490,10 @@
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B90" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C90" s="1">
         <v>146</v>
@@ -4520,7 +4514,7 @@
         <v>9.69</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J90" s="6">
         <v>1057.17</v>
@@ -4534,10 +4528,10 @@
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" s="10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B91" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C91" s="1">
         <v>44</v>
@@ -4558,7 +4552,7 @@
         <v>15.95</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J91" s="6">
         <v>1136.1400000000001</v>
@@ -4572,10 +4566,10 @@
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" s="10" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B92" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C92" s="1">
         <v>45</v>
@@ -4596,7 +4590,7 @@
         <v>14.14</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J92" s="6">
         <v>1166.03</v>
@@ -4610,10 +4604,10 @@
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B93" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C93" s="1">
         <v>28</v>
@@ -4634,7 +4628,7 @@
         <v>20.86</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J93" s="6">
         <v>1201.18</v>
@@ -4648,10 +4642,10 @@
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" s="10" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B94" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C94" s="1">
         <v>61</v>
@@ -4672,7 +4666,7 @@
         <v>18.78</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J94" s="6">
         <v>1248.8699999999999</v>
@@ -4686,10 +4680,10 @@
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" s="10" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B95" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C95" s="1">
         <v>149</v>
@@ -4710,7 +4704,7 @@
         <v>16.18</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J95" s="6">
         <v>1287.0899999999999</v>
@@ -4724,10 +4718,10 @@
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" s="10" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B96" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C96" s="1">
         <v>53</v>
@@ -4748,7 +4742,7 @@
         <v>21.16</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J96" s="6">
         <v>1332.8</v>
@@ -4762,10 +4756,10 @@
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" s="10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B97" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C97" s="1">
         <v>32</v>
@@ -4786,7 +4780,7 @@
         <v>21.88</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J97" s="6">
         <v>1349.13</v>
@@ -4800,10 +4794,10 @@
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" s="10" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B98" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C98" s="1">
         <v>71</v>
@@ -4824,7 +4818,7 @@
         <v>23.85</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J98" s="6">
         <v>1401.26</v>
@@ -4838,10 +4832,10 @@
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B99" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C99" s="1">
         <v>24</v>
@@ -4862,7 +4856,7 @@
         <v>22.72</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J99" s="6">
         <v>1446.63</v>
@@ -4876,10 +4870,10 @@
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" s="10" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B100" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C100" s="1">
         <v>18</v>
@@ -4900,7 +4894,7 @@
         <v>27.77</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J100" s="6">
         <v>1450.98</v>
@@ -4914,10 +4908,10 @@
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" s="10" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B101" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C101" s="1">
         <v>80</v>
@@ -4938,7 +4932,7 @@
         <v>7.96</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J101" s="6">
         <v>1458.92</v>
@@ -4952,10 +4946,10 @@
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" s="10" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B102" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C102" s="1">
         <v>21</v>
@@ -4976,7 +4970,7 @@
         <v>30.84</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J102" s="6">
         <v>1465.85</v>
@@ -4990,10 +4984,10 @@
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" s="10" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B103" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C103" s="1">
         <v>19</v>
@@ -5014,7 +5008,7 @@
         <v>30</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J103" s="6">
         <v>1486.82</v>
@@ -5028,10 +5022,10 @@
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" s="10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B104" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C104" s="1">
         <v>43</v>
@@ -5052,7 +5046,7 @@
         <v>24.76</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J104" s="6">
         <v>1568.48</v>
@@ -5066,10 +5060,10 @@
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" s="10" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B105" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C105" s="1">
         <v>78</v>
@@ -5090,7 +5084,7 @@
         <v>15.77</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J105" s="6">
         <v>1578</v>
@@ -5104,10 +5098,10 @@
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" s="10" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B106" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C106" s="1">
         <v>85</v>
@@ -5128,7 +5122,7 @@
         <v>23.71</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J106" s="6">
         <v>1580.7</v>
@@ -5142,10 +5136,10 @@
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107" s="10" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B107" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C107" s="1">
         <v>15</v>
@@ -5166,7 +5160,7 @@
         <v>39.409999999999997</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J107" s="6">
         <v>1600.55</v>
@@ -5180,10 +5174,10 @@
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" s="10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B108" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C108" s="1">
         <v>312</v>
@@ -5204,7 +5198,7 @@
         <v>28.4</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J108" s="6">
         <v>1610.54</v>
@@ -5218,10 +5212,10 @@
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B109" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C109" s="1">
         <v>23</v>
@@ -5242,7 +5236,7 @@
         <v>26.96</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J109" s="6">
         <v>1618.69</v>
@@ -5256,10 +5250,10 @@
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" s="10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B110" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C110" s="1">
         <v>122</v>
@@ -5280,7 +5274,7 @@
         <v>22.95</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J110" s="6">
         <v>1621.55</v>
@@ -5294,10 +5288,10 @@
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" s="10" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B111" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C111" s="1">
         <v>77</v>
@@ -5318,7 +5312,7 @@
         <v>24.37</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J111" s="6">
         <v>1646.2</v>
@@ -5332,10 +5326,10 @@
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112" s="10" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B112" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C112" s="1">
         <v>10</v>
@@ -5356,7 +5350,7 @@
         <v>39.97</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J112" s="6">
         <v>1660.89</v>
@@ -5370,10 +5364,10 @@
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" s="10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B113" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C113" s="1">
         <v>15</v>
@@ -5394,7 +5388,7 @@
         <v>35.82</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J113" s="6">
         <v>1695.51</v>
@@ -5408,10 +5402,10 @@
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" s="10" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B114" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C114" s="1">
         <v>182</v>
@@ -5432,7 +5426,7 @@
         <v>24.87</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J114" s="6">
         <v>1744.37</v>
@@ -5446,10 +5440,10 @@
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" s="10" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B115" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C115" s="1">
         <v>149</v>
@@ -5470,7 +5464,7 @@
         <v>38.89</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J115" s="6">
         <v>1860.96</v>
@@ -5484,10 +5478,10 @@
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" s="10" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B116" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C116" s="1">
         <v>25</v>
@@ -5508,7 +5502,7 @@
         <v>26.64</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J116" s="6">
         <v>2042.39</v>
@@ -5522,10 +5516,10 @@
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" s="10" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B117" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C117" s="1">
         <v>138</v>
@@ -5546,7 +5540,7 @@
         <v>34.700000000000003</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J117" s="6">
         <v>2120.98</v>
@@ -5560,10 +5554,10 @@
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" s="10" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B118" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C118" s="1">
         <v>124</v>
@@ -5584,7 +5578,7 @@
         <v>28.69</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J118" s="6">
         <v>2201.39</v>
@@ -5598,10 +5592,10 @@
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" s="10" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B119" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C119" s="1">
         <v>16</v>
@@ -5622,7 +5616,7 @@
         <v>36.89</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J119" s="6">
         <v>2269.21</v>
@@ -5636,10 +5630,10 @@
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" s="10" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B120" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C120" s="1">
         <v>64</v>
@@ -5660,7 +5654,7 @@
         <v>35.69</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J120" s="6">
         <v>2423.7800000000002</v>
